--- a/design_tables/excel/CardEffect.xlsx
+++ b/design_tables/excel/CardEffect.xlsx
@@ -152,29 +152,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CardEffectTable" displayName="CardEffectTable" ref="A1:O16" headerRowCount="1">
-  <tableColumns count="15">
-    <tableColumn id="1" name="id"/>
-    <tableColumn id="2" name="effect_type"/>
-    <tableColumn id="3" name="value"/>
-    <tableColumn id="4" name="target"/>
-    <tableColumn id="5" name="target_source"/>
-    <tableColumn id="6" name="trigger_timing"/>
-    <tableColumn id="7" name="duration_type"/>
-    <tableColumn id="8" name="duration_value"/>
-    <tableColumn id="9" name="duration_apply_policy"/>
-    <tableColumn id="10" name="stack_initial"/>
-    <tableColumn id="11" name="stack_max"/>
-    <tableColumn id="12" name="stack_change_on_trigger"/>
-    <tableColumn id="13" name="expire_policy"/>
-    <tableColumn id="14" name="on_remove"/>
-    <tableColumn id="15" name="comment"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -592,7 +569,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>20</v>
@@ -643,7 +620,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>20</v>
@@ -694,7 +671,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
@@ -745,7 +722,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>20</v>
@@ -796,7 +773,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>20</v>
@@ -847,7 +824,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>20</v>
@@ -898,7 +875,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>20</v>
@@ -949,7 +926,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>30</v>
@@ -1000,7 +977,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>30</v>
@@ -1051,7 +1028,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>30</v>
@@ -1102,7 +1079,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>30</v>
@@ -1153,7 +1130,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>50</v>
@@ -1198,9 +1175,8 @@
       <c r="B16" t="n">
         <v>0</v>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>50</v>
@@ -1240,8 +1216,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>